--- a/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
   <si>
     <t>WEST</t>
   </si>
@@ -656,212 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>192500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>215000</v>
+      </c>
+      <c r="F8" s="3">
         <v>219600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>430100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>205400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>227700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>230300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>223400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>186400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>190400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>181300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>171100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>155300</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>155200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>180100</v>
+      </c>
+      <c r="F9" s="3">
         <v>184500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>360200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>171100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>193400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>189200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>184500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>148000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>150700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>143000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>136800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>122200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>34900</v>
+      </c>
+      <c r="F10" s="3">
         <v>35100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>69900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>34300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>34300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>41100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>38900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>38400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>39700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>38300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>34300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>33100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +903,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +949,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,52 +999,64 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F14" s="3">
         <v>3100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>9500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>6600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>4400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>4000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>2300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>2500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>5100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>1800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1099,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1120,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>202600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>221300</v>
+      </c>
+      <c r="F17" s="3">
         <v>225000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>438800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>212800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>226700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>224800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>222100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>185600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>188400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>177200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>169500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>155200</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-8700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-7400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>5500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>4100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,228 +1240,260 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F20" s="3">
         <v>24600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-7000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>4800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-24100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-5500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F21" s="3">
         <v>25600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-16600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>5800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>7400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>7800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>9000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>10000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>7800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>6600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F22" s="3">
         <v>7800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>13400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>6000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>5200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>13400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>8800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>8000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>8300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>8600</v>
       </c>
       <c r="M22" s="3">
         <v>8300</v>
       </c>
       <c r="N22" s="3">
+        <v>8600</v>
+      </c>
+      <c r="O22" s="3">
+        <v>8300</v>
+      </c>
+      <c r="P22" s="3">
         <v>7400</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="F23" s="3">
         <v>11400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-29200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-8700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-28300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-13400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-7300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-6300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-6400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-6600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-7100</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F24" s="3">
         <v>-5200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-4400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>3600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-900</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1536,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F26" s="3">
         <v>16600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-31100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-4300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-31900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-13000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-5800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-5200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-6100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-6100</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F27" s="3">
         <v>12800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-27600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-4800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-32900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-20200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-12900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-11600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-11700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-10100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-12200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-12200</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1686,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1736,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1786,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1836,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-24600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>7000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-4800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>24100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>5500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F33" s="3">
         <v>12800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-27600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-4800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-32900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-20200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-12900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-11600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-11700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-10100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-12200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-12200</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1986,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F35" s="3">
         <v>12800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-27600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-4800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-32900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-20200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-12900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-11600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-11700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-10100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-12200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-12200</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2115,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,38 +2135,40 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>37200</v>
+      </c>
+      <c r="F41" s="3">
         <v>44400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>25200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>23700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>16800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>91000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>14300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>11900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2008,170 +2181,194 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F42" s="3">
         <v>15200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>18400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>13400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>15100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>13700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>15700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>18200</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>90200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>99200</v>
+      </c>
+      <c r="F43" s="3">
         <v>99600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>100900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>115500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>101600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>98400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>96000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>94400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>140400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>149900</v>
+      </c>
+      <c r="F44" s="3">
         <v>161300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>154700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>142600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>145800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>162200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>155300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>137600</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>13100</v>
+      </c>
+      <c r="F45" s="3">
         <v>19100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>17100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>15200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>18700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>14800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>12700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>14500</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2184,38 +2381,44 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>273200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>313100</v>
+      </c>
+      <c r="F46" s="3">
         <v>339600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>316200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>310300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>298100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>380100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>294100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>276600</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2228,8 +2431,14 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2266,102 +2475,120 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>464800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>411600</v>
+      </c>
+      <c r="F48" s="3">
         <v>302300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>255500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>210800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>196300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>145000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>143100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>143300</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>237100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>239100</v>
+      </c>
+      <c r="F49" s="3">
         <v>241400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>243400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>245100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>244900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>218000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>219600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>221300</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2631,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,38 +2681,44 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E52" s="3">
         <v>7800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="G52" s="3">
         <v>7200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>7100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>6900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>7000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>4700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>4200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2492,8 +2731,14 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,38 +2781,44 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>983300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>971500</v>
+      </c>
+      <c r="F54" s="3">
         <v>891100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>822300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>773300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>746200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>750100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>661400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>645400</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2580,8 +2831,14 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2855,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,82 +2875,90 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>69100</v>
+      </c>
+      <c r="F57" s="3">
         <v>62400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>102100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>101500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>116700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>110700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>117900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>98100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>125300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>131600</v>
+      </c>
+      <c r="F58" s="3">
         <v>129800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>84500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>52100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>54400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>73800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>76000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>61300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2704,38 +2971,44 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>38900</v>
+      </c>
+      <c r="F59" s="3">
         <v>30000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>43400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>40700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>45100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>41900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>37400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>43400</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2748,38 +3021,44 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>220300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>239600</v>
+      </c>
+      <c r="F60" s="3">
         <v>222200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>230000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>194400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>216100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>226400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>231300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>202800</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,38 +3071,44 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>273700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>223100</v>
+      </c>
+      <c r="F61" s="3">
         <v>205800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>237800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>215300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>162500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>164700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>310300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>311700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2836,38 +3121,44 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>123400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>120800</v>
+      </c>
+      <c r="F62" s="3">
         <v>62700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>93800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>75700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>80900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>59900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>31700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>34900</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2880,8 +3171,14 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3221,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3271,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,38 +3321,44 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>617400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>583600</v>
+      </c>
+      <c r="F66" s="3">
         <v>490600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>561500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>487900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>462000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>453700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>576200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>552300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3056,8 +3371,14 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3395,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3441,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,38 +3491,44 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>274100</v>
+      </c>
+      <c r="E70" s="3">
+        <v>274200</v>
+      </c>
+      <c r="F70" s="3">
         <v>274300</v>
       </c>
-      <c r="E70" s="3">
+      <c r="G70" s="3">
         <v>275000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="H70" s="3">
         <v>275100</v>
       </c>
-      <c r="G70" s="3">
+      <c r="I70" s="3">
         <v>274900</v>
       </c>
-      <c r="H70" s="3">
+      <c r="J70" s="3">
         <v>273600</v>
       </c>
-      <c r="I70" s="3">
+      <c r="K70" s="3">
         <v>295800</v>
       </c>
-      <c r="J70" s="3">
+      <c r="L70" s="3">
         <v>288600</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3206,8 +3541,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,38 +3591,44 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-386300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-362600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-342600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-359200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-332400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-328000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-296400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-276200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-263300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3294,8 +3641,14 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3691,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3741,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,38 +3791,44 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>113700</v>
+      </c>
+      <c r="F76" s="3">
         <v>126200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-14300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>10300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>9300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>22700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-210500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-195500</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3841,14 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3891,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F81" s="3">
         <v>12800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-27600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-4800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-32900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-20200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-12900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-11600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-11700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-10100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-12200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-12200</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +4020,60 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F83" s="3">
         <v>6400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>12100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>5900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>6400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>5800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>6000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>6000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>7100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>6100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>6100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>6200</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4116,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4166,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4216,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4266,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4316,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-39500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-35700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-25100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>2900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-12600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-8600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-38400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>11100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-7400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1300</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4390,60 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-43100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-65900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-36200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-19700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-40300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-7900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-6500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-8700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-12600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-4400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-4200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4486,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4536,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-43100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-67100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-58200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-22000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-54400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-6800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-5100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-7800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-10900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-4300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-3700</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4610,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4656,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4706,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4756,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,136 +4806,160 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>21100</v>
+      </c>
+      <c r="F100" s="3">
         <v>126800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>96400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>46400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-17500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>96900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>13600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>41700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>8500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>7700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>4400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>3200</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-200</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-100</v>
       </c>
       <c r="G101" s="3">
         <v>-200</v>
       </c>
       <c r="H101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="F102" s="3">
         <v>20000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>2400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-69100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>77400</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-4700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>8700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-4000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1700</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
   <si>
     <t>WEST</t>
   </si>
@@ -656,237 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>208400</v>
+      </c>
+      <c r="E8" s="3">
         <v>192500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>215000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>219600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>430100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>205400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>227700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>230300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>223400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>186400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>190400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>181300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>171100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>155300</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>167000</v>
+      </c>
+      <c r="E9" s="3">
         <v>155200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>180100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>184500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>360200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>171100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>193400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>189200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>184500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>148000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>150700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>143000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>136800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>122200</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E10" s="3">
         <v>37300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>34900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>35100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>69900</v>
-      </c>
-      <c r="H10" s="3">
-        <v>34300</v>
       </c>
       <c r="I10" s="3">
         <v>34300</v>
       </c>
       <c r="J10" s="3">
+        <v>34300</v>
+      </c>
+      <c r="K10" s="3">
         <v>41100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>38900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>38400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>39700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>34300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>33100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,58 +1022,64 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>9500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>224800</v>
+      </c>
+      <c r="E17" s="3">
         <v>202600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>221300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>225000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>438800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>212800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>226700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>224800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>222100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>185600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>188400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>177200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>169500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>155200</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,258 +1275,274 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>24600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-24100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-100</v>
       </c>
       <c r="N20" s="3">
         <v>-100</v>
       </c>
       <c r="O20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>25600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E22" s="3">
         <v>7600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7400</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-29200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-28300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E24" s="3">
         <v>5800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-5200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-900</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-20000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3900</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-6100</v>
       </c>
       <c r="P26" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
+      <c r="Q26" s="3">
+        <v>-6100</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-20000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-27600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-32900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10100</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-12200</v>
       </c>
       <c r="P27" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
+      <c r="Q27" s="3">
+        <v>-12200</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-24600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>24100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>100</v>
       </c>
       <c r="N32" s="3">
         <v>100</v>
       </c>
       <c r="O32" s="3">
+        <v>100</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-20000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-27600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-32900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-20200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10100</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-12200</v>
       </c>
       <c r="P33" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
+      <c r="Q33" s="3">
+        <v>-12200</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-20000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-27600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-32900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-20200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10100</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-12200</v>
       </c>
       <c r="P35" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
+      <c r="Q35" s="3">
+        <v>-12200</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,41 +2223,42 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E41" s="3">
         <v>12600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>37200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>44400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>91000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11900</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2187,41 +2274,44 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E42" s="3">
         <v>15400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>18400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>15100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>13700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>15700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18200</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2231,47 +2321,50 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>102100</v>
+      </c>
+      <c r="E43" s="3">
         <v>90200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>99200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>99600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>115500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>101600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>98400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>96000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>94400</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2281,47 +2374,50 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>163700</v>
+      </c>
+      <c r="E44" s="3">
         <v>140400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>149900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>161300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>154700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>142600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>145800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>162200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>155300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>137600</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2331,47 +2427,50 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E45" s="3">
         <v>14700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>19100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>17100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14500</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2387,41 +2486,44 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>332500</v>
+      </c>
+      <c r="E46" s="3">
         <v>273200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>313100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>339600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>316200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>310300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>298100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>380100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>294100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>276600</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2437,8 +2539,11 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2481,47 +2586,50 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>0</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>480900</v>
+      </c>
+      <c r="E48" s="3">
         <v>464800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>411600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>302300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>255500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>210800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>196300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>145000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>143100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>143300</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2531,47 +2639,50 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>235100</v>
+      </c>
+      <c r="E49" s="3">
         <v>237100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>239100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>241400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>243400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>245100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>244900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>218000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>219600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>221300</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2581,14 +2692,17 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,41 +2804,44 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E52" s="3">
         <v>8100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>7800</v>
       </c>
       <c r="F52" s="3">
         <v>7800</v>
       </c>
       <c r="G52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="H52" s="3">
         <v>7200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,41 +2910,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1056400</v>
+      </c>
+      <c r="E54" s="3">
         <v>983300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>971500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>891100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>822300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>773300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>746200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>750100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>661400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>645400</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2837,8 +2963,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,41 +3007,42 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E57" s="3">
         <v>44200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>69100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>62400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>102100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>101500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>116700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>110700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>117900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>98100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2921,47 +3052,50 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E58" s="3">
         <v>125300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>131600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>129800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>84500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>52100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>54400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>73800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>76000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>61300</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,41 +3111,44 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E59" s="3">
         <v>50800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>38900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>30000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>43400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>40700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>45100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>41900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>37400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>43400</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,41 +3164,44 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>253900</v>
+      </c>
+      <c r="E60" s="3">
         <v>220300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>239600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>222200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>230000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>194400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>216100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>226400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>231300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>202800</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3077,41 +3217,44 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>329900</v>
+      </c>
+      <c r="E61" s="3">
         <v>273700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>223100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>205800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>237800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>215300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>162500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>164700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>310300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>311700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3127,41 +3270,44 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E62" s="3">
         <v>123400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>120800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>62700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>93800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>75700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>80900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>59900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>31700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>34900</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3177,8 +3323,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,41 +3482,44 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>700800</v>
+      </c>
+      <c r="E66" s="3">
         <v>617400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>583600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>490600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>561500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>487900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>462000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>453700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>576200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>552300</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3377,8 +3535,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,41 +3662,44 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>274000</v>
+      </c>
+      <c r="E70" s="3">
         <v>274100</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>274200</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>274300</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>275000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>275100</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>274900</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>273600</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>295800</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>288600</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,41 +3768,44 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-404100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-386300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-362600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-342600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-359200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-332400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-328000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-296400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-276200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-263300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3821,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,41 +3980,44 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>81500</v>
+      </c>
+      <c r="E76" s="3">
         <v>91700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>113700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>126200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-14300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-210500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-195500</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3847,8 +4033,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-20000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-27600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-32900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-20200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10100</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-12200</v>
       </c>
       <c r="P81" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
+      <c r="Q81" s="3">
+        <v>-12200</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,58 +4220,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E83" s="3">
         <v>7500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>6000</v>
       </c>
       <c r="L83" s="3">
         <v>6000</v>
       </c>
       <c r="M83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N83" s="3">
         <v>7100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>6100</v>
       </c>
       <c r="O83" s="3">
         <v>6100</v>
       </c>
       <c r="P83" s="3">
+        <v>6100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>6200</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E89" s="3">
         <v>8000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-39500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-35700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-25100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-38400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,58 +4612,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-69000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-43100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-65900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-36200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-40300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-68900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-43100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-67100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-58200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-54400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,154 +5055,166 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E100" s="3">
         <v>37000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>21100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>126800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>96400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>46400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-17500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>96900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>13600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>41700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>8500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3200</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3">
         <v>-200</v>
       </c>
       <c r="H101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-200</v>
       </c>
       <c r="J101" s="3">
         <v>-200</v>
       </c>
       <c r="K101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-24100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>20000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-69100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>77400</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-4700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>WEST</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>220900</v>
+      </c>
+      <c r="E8" s="3">
         <v>208400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>192500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>215000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>219600</v>
       </c>
-      <c r="H8" s="3">
-        <v>430100</v>
-      </c>
       <c r="I8" s="3">
+        <v>224700</v>
+      </c>
+      <c r="J8" s="3">
         <v>205400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>227700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>230300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>223400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>186400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>190400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>181300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>171100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>155300</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E9" s="3">
         <v>167000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>155200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>180100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>184500</v>
       </c>
-      <c r="H9" s="3">
-        <v>360200</v>
-      </c>
       <c r="I9" s="3">
+        <v>189000</v>
+      </c>
+      <c r="J9" s="3">
         <v>171100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>193400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>189200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>184500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>148000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>150700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>143000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>136800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>122200</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E10" s="3">
         <v>41400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>37300</v>
       </c>
-      <c r="F10" s="3">
-        <v>34900</v>
-      </c>
       <c r="G10" s="3">
+        <v>34800</v>
+      </c>
+      <c r="H10" s="3">
         <v>35100</v>
       </c>
-      <c r="H10" s="3">
-        <v>69900</v>
-      </c>
       <c r="I10" s="3">
-        <v>34300</v>
+        <v>35700</v>
       </c>
       <c r="J10" s="3">
         <v>34300</v>
       </c>
       <c r="K10" s="3">
+        <v>34300</v>
+      </c>
+      <c r="L10" s="3">
         <v>41100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>38900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>38400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>39700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>38300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>34300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>33100</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,84 +1042,90 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>5200</v>
+        <v>3700</v>
       </c>
       <c r="E14" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F14" s="3">
         <v>3000</v>
       </c>
-      <c r="F14" s="3">
-        <v>1900</v>
-      </c>
       <c r="G14" s="3">
-        <v>3100</v>
+        <v>2400</v>
       </c>
       <c r="H14" s="3">
-        <v>9500</v>
+        <v>3400</v>
       </c>
       <c r="I14" s="3">
-        <v>6600</v>
+        <v>2900</v>
       </c>
       <c r="J14" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K14" s="3">
         <v>4400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>229900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>218600</v>
+      </c>
+      <c r="F17" s="3">
+        <v>199700</v>
+      </c>
+      <c r="G17" s="3">
+        <v>218900</v>
+      </c>
+      <c r="H17" s="3">
+        <v>221600</v>
+      </c>
+      <c r="I17" s="3">
+        <v>223100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>205300</v>
+      </c>
+      <c r="K17" s="3">
+        <v>226700</v>
+      </c>
+      <c r="L17" s="3">
         <v>224800</v>
       </c>
-      <c r="E17" s="3">
-        <v>202600</v>
-      </c>
-      <c r="F17" s="3">
-        <v>221300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>225000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>438800</v>
-      </c>
-      <c r="I17" s="3">
-        <v>212800</v>
-      </c>
-      <c r="J17" s="3">
-        <v>226700</v>
-      </c>
-      <c r="K17" s="3">
-        <v>224800</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>222100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>185600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>188400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>177200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>169500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>155200</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-16400</v>
+        <v>-9000</v>
       </c>
       <c r="E18" s="3">
-        <v>-10100</v>
+        <v>-10200</v>
       </c>
       <c r="F18" s="3">
-        <v>-6300</v>
+        <v>-7200</v>
       </c>
       <c r="G18" s="3">
-        <v>-5400</v>
+        <v>-3900</v>
       </c>
       <c r="H18" s="3">
-        <v>-8700</v>
+        <v>-2000</v>
       </c>
       <c r="I18" s="3">
-        <v>-7400</v>
+        <v>1600</v>
       </c>
       <c r="J18" s="3">
+        <v>200</v>
+      </c>
+      <c r="K18" s="3">
         <v>1000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,273 +1309,289 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1500</v>
+        <v>-5500</v>
       </c>
       <c r="E20" s="3">
-        <v>-100</v>
+        <v>-1500</v>
       </c>
       <c r="F20" s="3">
-        <v>-8800</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>24600</v>
+        <v>8800</v>
       </c>
       <c r="H20" s="3">
-        <v>-7000</v>
+        <v>-24600</v>
       </c>
       <c r="I20" s="3">
-        <v>4800</v>
+        <v>11900</v>
       </c>
       <c r="J20" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="K20" s="3">
         <v>-24100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-100</v>
       </c>
       <c r="O20" s="3">
         <v>-100</v>
       </c>
       <c r="P20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-6900</v>
+        <v>4100</v>
       </c>
       <c r="E21" s="3">
-        <v>-2700</v>
+        <v>-800</v>
       </c>
       <c r="F21" s="3">
-        <v>-7000</v>
+        <v>200</v>
       </c>
       <c r="G21" s="3">
-        <v>25600</v>
+        <v>-4500</v>
       </c>
       <c r="H21" s="3">
-        <v>-3700</v>
+        <v>29000</v>
       </c>
       <c r="I21" s="3">
-        <v>3200</v>
+        <v>-4100</v>
       </c>
       <c r="J21" s="3">
+        <v>10800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-16600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6600</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E22" s="3">
         <v>7500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="J22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="L22" s="3">
         <v>13400</v>
       </c>
-      <c r="I22" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>5200</v>
-      </c>
-      <c r="K22" s="3">
-        <v>13400</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7400</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-22300</v>
+        <v>-14200</v>
       </c>
       <c r="E23" s="3">
-        <v>-17800</v>
+        <v>-22400</v>
       </c>
       <c r="F23" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="G23" s="3">
         <v>-23100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11400</v>
       </c>
-      <c r="H23" s="3">
-        <v>-29200</v>
-      </c>
       <c r="I23" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="J23" s="3">
         <v>-8700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-28300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7100</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-5200</v>
       </c>
-      <c r="H24" s="3">
-        <v>1900</v>
-      </c>
       <c r="I24" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J24" s="3">
         <v>-4400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-900</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-17700</v>
+        <v>-14300</v>
       </c>
       <c r="E26" s="3">
-        <v>-23600</v>
+        <v>-17800</v>
       </c>
       <c r="F26" s="3">
-        <v>-20000</v>
+        <v>-23700</v>
       </c>
       <c r="G26" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="H26" s="3">
         <v>16600</v>
       </c>
-      <c r="H26" s="3">
-        <v>-31100</v>
-      </c>
       <c r="I26" s="3">
+        <v>-26800</v>
+      </c>
+      <c r="J26" s="3">
         <v>-4300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-31900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3900</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-6100</v>
       </c>
       <c r="Q26" s="3">
         <v>-6100</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
+      <c r="R26" s="3">
+        <v>-6100</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-20000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12800</v>
       </c>
-      <c r="H27" s="3">
-        <v>-27600</v>
-      </c>
       <c r="I27" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="J27" s="3">
         <v>-4800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-32900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10100</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-12200</v>
       </c>
       <c r="Q27" s="3">
         <v>-12200</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
+      <c r="R27" s="3">
+        <v>-12200</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1500</v>
+        <v>5500</v>
       </c>
       <c r="E32" s="3">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="F32" s="3">
-        <v>8800</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>-24600</v>
+        <v>-8800</v>
       </c>
       <c r="H32" s="3">
-        <v>7000</v>
+        <v>24600</v>
       </c>
       <c r="I32" s="3">
-        <v>-4800</v>
+        <v>-11900</v>
       </c>
       <c r="J32" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K32" s="3">
         <v>24100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>100</v>
       </c>
       <c r="O32" s="3">
         <v>100</v>
       </c>
       <c r="P32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-17700</v>
+        <v>-14300</v>
       </c>
       <c r="E33" s="3">
-        <v>-23600</v>
+        <v>-17800</v>
       </c>
       <c r="F33" s="3">
-        <v>-20000</v>
+        <v>-23700</v>
       </c>
       <c r="G33" s="3">
-        <v>12800</v>
+        <v>-20100</v>
       </c>
       <c r="H33" s="3">
-        <v>-27600</v>
+        <v>16600</v>
       </c>
       <c r="I33" s="3">
-        <v>-4800</v>
+        <v>-26800</v>
       </c>
       <c r="J33" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-32900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10100</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-12200</v>
       </c>
       <c r="Q33" s="3">
         <v>-12200</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
+      <c r="R33" s="3">
+        <v>-12200</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-17700</v>
+        <v>-14300</v>
       </c>
       <c r="E35" s="3">
-        <v>-23600</v>
+        <v>-17800</v>
       </c>
       <c r="F35" s="3">
-        <v>-20000</v>
+        <v>-23700</v>
       </c>
       <c r="G35" s="3">
-        <v>12800</v>
+        <v>-20100</v>
       </c>
       <c r="H35" s="3">
-        <v>-27600</v>
+        <v>16600</v>
       </c>
       <c r="I35" s="3">
-        <v>-4800</v>
+        <v>-26800</v>
       </c>
       <c r="J35" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-32900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10100</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-12200</v>
       </c>
       <c r="Q35" s="3">
         <v>-12200</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
+      <c r="R35" s="3">
+        <v>-12200</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,44 +2310,45 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E41" s="3">
         <v>24300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>37200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>44400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>91000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2277,44 +2364,47 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>17800</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>15400</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>15100</v>
+      </c>
+      <c r="L42" s="3">
         <v>13700</v>
       </c>
-      <c r="G42" s="3">
-        <v>15200</v>
-      </c>
-      <c r="H42" s="3">
-        <v>18400</v>
-      </c>
-      <c r="I42" s="3">
-        <v>13400</v>
-      </c>
-      <c r="J42" s="3">
-        <v>15100</v>
-      </c>
-      <c r="K42" s="3">
-        <v>13700</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>15700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>18200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2324,50 +2414,53 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>102700</v>
+      </c>
+      <c r="E43" s="3">
         <v>102100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>90200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>99200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>99600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>100900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>115500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>101600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>98400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>96000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>94400</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2377,50 +2470,53 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>160600</v>
+      </c>
+      <c r="E44" s="3">
         <v>163700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>140400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>149900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>161300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>154700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>142600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>145800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>162200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>155300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>137600</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2430,50 +2526,53 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>24700</v>
+        <v>16700</v>
       </c>
       <c r="E45" s="3">
-        <v>14700</v>
+        <v>26900</v>
       </c>
       <c r="F45" s="3">
-        <v>13100</v>
+        <v>15400</v>
       </c>
       <c r="G45" s="3">
-        <v>19100</v>
+        <v>14000</v>
       </c>
       <c r="H45" s="3">
-        <v>17100</v>
+        <v>15200</v>
       </c>
       <c r="I45" s="3">
-        <v>15200</v>
+        <v>18400</v>
       </c>
       <c r="J45" s="3">
+        <v>13400</v>
+      </c>
+      <c r="K45" s="3">
         <v>18700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14500</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,44 +2588,47 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>336600</v>
+      </c>
+      <c r="E46" s="3">
         <v>332500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>273200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>313100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>339600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>316200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>310300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>298100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>380100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>294100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>276600</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2542,31 +2644,34 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
+        <v>1000</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2589,50 +2694,53 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E48" s="3">
         <v>480900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>464800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>411600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>302300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>255500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>210800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>196300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>145000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>143100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>143300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2642,50 +2750,53 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>233100</v>
+      </c>
+      <c r="E49" s="3">
         <v>235100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>237100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>239100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>241400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>243400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>245100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>244900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>218000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>219600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>221300</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2695,14 +2806,17 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,44 +2924,47 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7900</v>
+        <v>5400</v>
       </c>
       <c r="E52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F52" s="3">
         <v>8100</v>
       </c>
-      <c r="F52" s="3">
-        <v>7800</v>
-      </c>
       <c r="G52" s="3">
-        <v>7800</v>
+        <v>3100</v>
       </c>
       <c r="H52" s="3">
-        <v>7200</v>
+        <v>3000</v>
       </c>
       <c r="I52" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J52" s="3">
         <v>7100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,44 +3036,47 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1077100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1056400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>983300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>971500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>891100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>822300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>773300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>746200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>750100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>661400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>645400</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2966,8 +3092,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,44 +3138,45 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E57" s="3">
         <v>43100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>44200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>69100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>62400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>102100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>101500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>116700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>110700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>117900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>98100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3055,50 +3186,53 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>143000</v>
+        <v>146600</v>
       </c>
       <c r="E58" s="3">
-        <v>125300</v>
+        <v>148600</v>
       </c>
       <c r="F58" s="3">
-        <v>131600</v>
+        <v>133300</v>
       </c>
       <c r="G58" s="3">
-        <v>129800</v>
+        <v>144700</v>
       </c>
       <c r="H58" s="3">
-        <v>84500</v>
+        <v>139100</v>
       </c>
       <c r="I58" s="3">
-        <v>52100</v>
+        <v>97100</v>
       </c>
       <c r="J58" s="3">
+        <v>65500</v>
+      </c>
+      <c r="K58" s="3">
         <v>54400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>73800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>76000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>61300</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3114,44 +3248,47 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>67800</v>
+        <v>10200</v>
       </c>
       <c r="E59" s="3">
-        <v>50800</v>
+        <v>5000</v>
       </c>
       <c r="F59" s="3">
-        <v>38900</v>
+        <v>4200</v>
       </c>
       <c r="G59" s="3">
-        <v>30000</v>
+        <v>3700</v>
       </c>
       <c r="H59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I59" s="3">
+        <v>7300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K59" s="3">
+        <v>45100</v>
+      </c>
+      <c r="L59" s="3">
+        <v>41900</v>
+      </c>
+      <c r="M59" s="3">
+        <v>37400</v>
+      </c>
+      <c r="N59" s="3">
         <v>43400</v>
       </c>
-      <c r="I59" s="3">
-        <v>40700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>45100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>41900</v>
-      </c>
-      <c r="L59" s="3">
-        <v>37400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>43400</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3167,44 +3304,47 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E60" s="3">
         <v>253900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>220300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>239600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>222200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>230000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>194400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>216100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>226400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>231300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>202800</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3220,44 +3360,47 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>329900</v>
+        <v>434300</v>
       </c>
       <c r="E61" s="3">
-        <v>273700</v>
+        <v>389200</v>
       </c>
       <c r="F61" s="3">
-        <v>223100</v>
+        <v>334100</v>
       </c>
       <c r="G61" s="3">
-        <v>205800</v>
+        <v>286600</v>
       </c>
       <c r="H61" s="3">
-        <v>237800</v>
+        <v>217500</v>
       </c>
       <c r="I61" s="3">
-        <v>215300</v>
+        <v>250200</v>
       </c>
       <c r="J61" s="3">
+        <v>228500</v>
+      </c>
+      <c r="K61" s="3">
         <v>162500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>164700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>310300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>311700</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3273,44 +3416,47 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>117000</v>
+        <v>2000</v>
       </c>
       <c r="E62" s="3">
-        <v>123400</v>
+        <v>44400</v>
       </c>
       <c r="F62" s="3">
-        <v>120800</v>
+        <v>46300</v>
       </c>
       <c r="G62" s="3">
-        <v>62700</v>
+        <v>46400</v>
       </c>
       <c r="H62" s="3">
-        <v>93800</v>
+        <v>38300</v>
       </c>
       <c r="I62" s="3">
-        <v>75700</v>
+        <v>63400</v>
       </c>
       <c r="J62" s="3">
+        <v>51600</v>
+      </c>
+      <c r="K62" s="3">
         <v>80900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>59900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>31700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>34900</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,44 +3640,47 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>692800</v>
+      </c>
+      <c r="E66" s="3">
         <v>700800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>617400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>583600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>490600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>561500</v>
       </c>
-      <c r="I66" s="3">
-        <v>487900</v>
-      </c>
       <c r="J66" s="3">
+        <v>485400</v>
+      </c>
+      <c r="K66" s="3">
         <v>462000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>453700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>576200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>552300</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3538,8 +3696,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,44 +3830,47 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>273900</v>
+      </c>
+      <c r="E70" s="3">
         <v>274000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>274100</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>274200</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>274300</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>275000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>275100</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>274900</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>273600</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>295800</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>288600</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,44 +3942,47 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-418300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-404100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-386300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-362600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-342600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-359200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-332400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-328000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-296400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-276200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-263300</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3824,8 +3998,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,44 +4166,47 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>110300</v>
+      </c>
+      <c r="E76" s="3">
         <v>81500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>91700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>113700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>126200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-14300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-210500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-195500</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4036,8 +4222,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-17700</v>
+        <v>-14300</v>
       </c>
       <c r="E81" s="3">
-        <v>-23600</v>
+        <v>-17800</v>
       </c>
       <c r="F81" s="3">
-        <v>-20000</v>
+        <v>-23700</v>
       </c>
       <c r="G81" s="3">
-        <v>12800</v>
+        <v>-20100</v>
       </c>
       <c r="H81" s="3">
-        <v>-27600</v>
+        <v>16600</v>
       </c>
       <c r="I81" s="3">
-        <v>-4800</v>
+        <v>-26800</v>
       </c>
       <c r="J81" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-32900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10100</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-12200</v>
       </c>
       <c r="Q81" s="3">
         <v>-12200</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
+      <c r="R81" s="3">
+        <v>-12200</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,61 +4419,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8000</v>
+        <v>4400</v>
       </c>
       <c r="E83" s="3">
-        <v>7500</v>
+        <v>4200</v>
       </c>
       <c r="F83" s="3">
-        <v>8200</v>
+        <v>3900</v>
       </c>
       <c r="G83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K83" s="3">
         <v>6400</v>
       </c>
-      <c r="H83" s="3">
-        <v>12100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>5900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>6400</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>6000</v>
       </c>
       <c r="M83" s="3">
         <v>6000</v>
       </c>
       <c r="N83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="O83" s="3">
         <v>7100</v>
-      </c>
-      <c r="O83" s="3">
-        <v>6100</v>
       </c>
       <c r="P83" s="3">
         <v>6100</v>
       </c>
       <c r="Q83" s="3">
+        <v>6100</v>
+      </c>
+      <c r="R83" s="3">
         <v>6200</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-23700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-39500</v>
       </c>
-      <c r="H89" s="3">
-        <v>-35700</v>
-      </c>
       <c r="I89" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="J89" s="3">
         <v>-25100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-38400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>11100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1300</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,8 +4833,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4622,52 +4843,55 @@
         <v>-36300</v>
       </c>
       <c r="E91" s="3">
-        <v>-69000</v>
+        <v>-36200</v>
       </c>
       <c r="F91" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="G91" s="3">
         <v>-43100</v>
       </c>
-      <c r="G91" s="3">
-        <v>-65900</v>
-      </c>
       <c r="H91" s="3">
-        <v>-36200</v>
+        <v>-65800</v>
       </c>
       <c r="I91" s="3">
-        <v>-19700</v>
+        <v>-36100</v>
       </c>
       <c r="J91" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-40300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4200</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-35800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-68900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-43100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-67100</v>
       </c>
-      <c r="H94" s="3">
-        <v>-58200</v>
-      </c>
       <c r="I94" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="J94" s="3">
         <v>-22000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-54400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3700</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,31 +5079,32 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,72 +5301,78 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E100" s="3">
         <v>71400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>37000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>21100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>126800</v>
       </c>
-      <c r="H100" s="3">
-        <v>96400</v>
-      </c>
       <c r="I100" s="3">
+        <v>50000</v>
+      </c>
+      <c r="J100" s="3">
         <v>46400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>96900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>13600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>41700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>8500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3200</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="E101" s="3">
         <v>-100</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G101" s="3">
         <v>-200</v>
@@ -5132,89 +5381,95 @@
         <v>-200</v>
       </c>
       <c r="I101" s="3">
+        <v>100</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-200</v>
       </c>
       <c r="K101" s="3">
         <v>-200</v>
       </c>
       <c r="L101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E102" s="3">
         <v>12300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-24100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>20000</v>
       </c>
-      <c r="H102" s="3">
-        <v>2400</v>
-      </c>
       <c r="I102" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-69100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>77400</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-4700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1700</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>WEST</t>
   </si>
@@ -656,263 +656,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>229000</v>
+      </c>
+      <c r="E8" s="3">
         <v>220900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>208400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>192500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>215000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>219600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>224700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>205400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>227700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>230300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>223400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>186400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>190400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>181300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>171100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>155300</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E9" s="3">
         <v>183800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>167000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>155200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>180100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>184500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>189000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>171100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>193400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>189200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>184500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>148000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>150700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>143000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>136800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>122200</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E10" s="3">
         <v>37100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>41400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>37300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>34800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>35100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>35700</v>
-      </c>
-      <c r="J10" s="3">
-        <v>34300</v>
       </c>
       <c r="K10" s="3">
         <v>34300</v>
       </c>
       <c r="L10" s="3">
+        <v>34300</v>
+      </c>
+      <c r="M10" s="3">
         <v>41100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>38900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>39700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>38300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>34300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>33100</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +945,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,91 +1061,97 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E14" s="3">
         <v>3700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E15" s="3">
         <v>7700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1157,8 +1179,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>233900</v>
+      </c>
+      <c r="E17" s="3">
         <v>229900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>218600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>199700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>218900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>221600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>223100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>205300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>226700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>224800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>222100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>185600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>188400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>177200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>169500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>155200</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,288 +1342,304 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-24600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>11900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-24100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-100</v>
       </c>
       <c r="P20" s="3">
         <v>-100</v>
       </c>
       <c r="Q20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E21" s="3">
         <v>4100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>29000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-16600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E22" s="3">
         <v>6900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7400</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-22400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-23100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-20600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7100</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-5200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-900</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-20100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3900</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-6100</v>
       </c>
       <c r="R26" s="3">
         <v>-6100</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>-6100</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-20000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-22800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-32900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10100</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-12200</v>
       </c>
       <c r="R27" s="3">
         <v>-12200</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>-12200</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2048,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>5500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>24600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-11900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>24100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>100</v>
       </c>
       <c r="P32" s="3">
         <v>100</v>
       </c>
       <c r="Q32" s="3">
+        <v>100</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-20100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-26800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-32900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10100</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-12200</v>
       </c>
       <c r="R33" s="3">
         <v>-12200</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>-12200</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-20100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-26800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-32900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10100</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-12200</v>
       </c>
       <c r="R35" s="3">
         <v>-12200</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>-12200</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,47 +2396,48 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E41" s="3">
         <v>22400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>24300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>44400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>91000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,8 +2453,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2394,20 +2483,20 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>15100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>15700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>18200</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2417,53 +2506,56 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100800</v>
+      </c>
+      <c r="E43" s="3">
         <v>102700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>102100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>90200</v>
       </c>
-      <c r="G43" s="3">
-        <v>99200</v>
-      </c>
       <c r="H43" s="3">
+        <v>99500</v>
+      </c>
+      <c r="I43" s="3">
         <v>99600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>115500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>101600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>98400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>96000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>94400</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2473,53 +2565,56 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>163300</v>
+      </c>
+      <c r="E44" s="3">
         <v>160600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>163700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>140400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>149900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>161300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>154700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>142600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>145800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>162200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>155300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>137600</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2529,53 +2624,56 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E45" s="3">
         <v>16700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15400</v>
       </c>
-      <c r="G45" s="3">
-        <v>14000</v>
-      </c>
       <c r="H45" s="3">
+        <v>13700</v>
+      </c>
+      <c r="I45" s="3">
         <v>15200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>18700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14500</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2591,47 +2689,50 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>333600</v>
+      </c>
+      <c r="E46" s="3">
         <v>336600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>332500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>273200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>313100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>339600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>316200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>310300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>298100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>380100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>294100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>276600</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,34 +2748,37 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="E47" s="3">
         <v>1000</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="F47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>1500</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2697,53 +2801,56 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>0</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>530400</v>
+      </c>
+      <c r="E48" s="3">
         <v>500000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>480900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>464800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>411600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>302300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>255500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>210800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>196300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>145000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>143100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>143300</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2753,53 +2860,56 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>231000</v>
+      </c>
+      <c r="E49" s="3">
         <v>233100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>235100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>237100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>239100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>241400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>243400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>245100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>244900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>218000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>219600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>221300</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2809,14 +2919,17 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,47 +3043,50 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E52" s="3">
         <v>5400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8100</v>
       </c>
-      <c r="G52" s="3">
-        <v>3100</v>
-      </c>
       <c r="H52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="I52" s="3">
         <v>3000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2983,8 +3102,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,47 +3161,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1101800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1077100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1056400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>983300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>971500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>891100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>822300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>773300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>746200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>750100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>661400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>645400</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,8 +3220,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,47 +3268,48 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E57" s="3">
         <v>52300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>43100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>44200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>69100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>62400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>102100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>101500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>116700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>110700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>117900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>98100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3189,53 +3319,56 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>152600</v>
+      </c>
+      <c r="E58" s="3">
         <v>146600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>148600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>133300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>144700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>139100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>97100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>65500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>54400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>73800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>76000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>61300</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3251,47 +3384,50 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E59" s="3">
         <v>10200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>45100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>41900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>37400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>43400</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3307,47 +3443,50 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>277900</v>
+      </c>
+      <c r="E60" s="3">
         <v>242000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>253900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>220300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>239600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>222200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>230000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>194400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>216100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>226400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>231300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>202800</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3363,47 +3502,50 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>436300</v>
+      </c>
+      <c r="E61" s="3">
         <v>434300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>389200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>334100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>286600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>217500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>250200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>228500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>162500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>164700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>310300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>311700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3419,47 +3561,50 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>44400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>46300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>46400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>38300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>63400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>51600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>80900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>59900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>31700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>34900</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3475,8 +3620,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,47 +3797,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>730400</v>
+      </c>
+      <c r="E66" s="3">
         <v>692800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>700800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>617400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>583600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>490600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>561500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>485400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>462000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>453700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>576200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>552300</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3699,8 +3856,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3842,38 +4009,38 @@
         <v>273900</v>
       </c>
       <c r="E70" s="3">
+        <v>273900</v>
+      </c>
+      <c r="F70" s="3">
         <v>274000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>274100</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>274200</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>274300</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>275000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>275100</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>274900</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>273600</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>295800</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>288600</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3889,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,47 +4115,50 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-442900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-418300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-404100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-386300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-362600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-342600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-359200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-332400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-328000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-296400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-276200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-263300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,8 +4174,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,47 +4351,50 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>97500</v>
+      </c>
+      <c r="E76" s="3">
         <v>110300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>81500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>91700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>113700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>126200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-14300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-210500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-195500</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4225,8 +4410,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-20100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-26800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-32900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10100</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-12200</v>
       </c>
       <c r="R81" s="3">
         <v>-12200</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>-12200</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,64 +4617,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4300</v>
       </c>
       <c r="J83" s="3">
         <v>4300</v>
       </c>
       <c r="K83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="L83" s="3">
         <v>6400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5800</v>
-      </c>
-      <c r="M83" s="3">
-        <v>6000</v>
       </c>
       <c r="N83" s="3">
         <v>6000</v>
       </c>
       <c r="O83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="P83" s="3">
         <v>7100</v>
-      </c>
-      <c r="P83" s="3">
-        <v>6100</v>
       </c>
       <c r="Q83" s="3">
         <v>6100</v>
       </c>
       <c r="R83" s="3">
+        <v>6100</v>
+      </c>
+      <c r="S83" s="3">
         <v>6200</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-23700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-39500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-25100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-12600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-38400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,64 +5053,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-36300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-36200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-68900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-43100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-65800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-40300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4200</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5228,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-35600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-68900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-43100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-67100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-36100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-54400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3700</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5106,8 +5339,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5136,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,172 +5546,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E100" s="3">
         <v>43000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>71400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>37000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>126800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>50000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>46400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-17500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>96900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>41700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>8500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>7700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-100</v>
       </c>
       <c r="F101" s="3">
         <v>-100</v>
       </c>
       <c r="G101" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="H101" s="3">
         <v>-200</v>
       </c>
       <c r="I101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-200</v>
       </c>
       <c r="L101" s="3">
         <v>-200</v>
       </c>
       <c r="M101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E102" s="3">
         <v>6700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-24100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>20000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-69100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>77400</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-4700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1700</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>WEST</t>
   </si>
@@ -656,275 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>213800</v>
+      </c>
+      <c r="E8" s="3">
         <v>229000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>220900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>208400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>192500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>215000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>219600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>224700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>205400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>227700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>230300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>223400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>186400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>190400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>181300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>171100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>155300</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>184700</v>
+      </c>
+      <c r="E9" s="3">
         <v>191000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>183800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>167000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>155200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>180100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>184500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>189000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>171100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>193400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>189200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>184500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>148000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>150700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>143000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>136800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>122200</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E10" s="3">
         <v>38000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>37100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>41400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>37300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>34800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>35100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>35700</v>
-      </c>
-      <c r="K10" s="3">
-        <v>34300</v>
       </c>
       <c r="L10" s="3">
         <v>34300</v>
       </c>
       <c r="M10" s="3">
+        <v>34300</v>
+      </c>
+      <c r="N10" s="3">
         <v>41100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>38400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>39700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>38300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>34300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>33100</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1005,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,97 +1081,103 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E14" s="3">
         <v>4900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E15" s="3">
         <v>11500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>225100</v>
+      </c>
+      <c r="E17" s="3">
         <v>233900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>229900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>218600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>199700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>218900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>221600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>223100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>205300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>226700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>224800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>222100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>185600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>188400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>177200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>169500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>155200</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,303 +1376,319 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-24600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>11900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-24100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-100</v>
       </c>
       <c r="Q20" s="3">
         <v>-100</v>
       </c>
       <c r="R20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>800</v>
+      </c>
+      <c r="E21" s="3">
         <v>6300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>29000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>10000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6600</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E22" s="3">
         <v>11900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7400</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-22100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-22400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-23100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-20600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E24" s="3">
         <v>2500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-5200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-900</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-24600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-14300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3900</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-6100</v>
       </c>
       <c r="S26" s="3">
         <v>-6100</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+      <c r="T26" s="3">
+        <v>-6100</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-22800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-32900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10100</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-12200</v>
       </c>
       <c r="S27" s="3">
         <v>-12200</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+      <c r="T27" s="3">
+        <v>-12200</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>24600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-11900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>24100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="P32" s="3">
-        <v>100</v>
       </c>
       <c r="Q32" s="3">
         <v>100</v>
       </c>
       <c r="R32" s="3">
+        <v>100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-14300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-32900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10100</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-12200</v>
       </c>
       <c r="S33" s="3">
         <v>-12200</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+      <c r="T33" s="3">
+        <v>-12200</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-14300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-32900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10100</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-12200</v>
       </c>
       <c r="S35" s="3">
         <v>-12200</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+      <c r="T35" s="3">
+        <v>-12200</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,50 +2483,51 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E41" s="3">
         <v>26200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>24300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>37200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>44400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>91000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2456,8 +2543,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2486,20 +2576,20 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>15100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>13700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>15700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>18200</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2509,56 +2599,59 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E43" s="3">
         <v>100800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>102700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>102100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>90200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>99500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>99600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>115500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>101600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>98400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>96000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>94400</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2568,56 +2661,59 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>187400</v>
+      </c>
+      <c r="E44" s="3">
         <v>163300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>160600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>163700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>140400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>149900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>161300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>154700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>142600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>145800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>162200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>155300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>137600</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2627,56 +2723,59 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E45" s="3">
         <v>19700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>18700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14500</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2692,50 +2791,53 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>363800</v>
+      </c>
+      <c r="E46" s="3">
         <v>333600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>336600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>332500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>273200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>313100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>339600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>316200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>310300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>298100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>380100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>294100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>276600</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2751,37 +2853,40 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1200</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1000</v>
       </c>
       <c r="F47" s="3">
         <v>1000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+      <c r="G47" s="3">
+        <v>1000</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>1500</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2804,56 +2909,59 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>539100</v>
+      </c>
+      <c r="E48" s="3">
         <v>530400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>500000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>480900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>464800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>411600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>302300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>255500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>210800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>196300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>145000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>143100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>143300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2863,56 +2971,59 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>229000</v>
+      </c>
+      <c r="E49" s="3">
         <v>231000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>233100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>235100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>237100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>239100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>241400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>243400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>245100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>244900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>218000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>219600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>221300</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2922,14 +3033,17 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,50 +3163,53 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E52" s="3">
         <v>4600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,50 +3287,53 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1138700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1101800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1077100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1056400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>983300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>971500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>891100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>822300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>773300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>746200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>750100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>661400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>645400</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3223,8 +3349,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,50 +3399,51 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E57" s="3">
         <v>84300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>52300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>43100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>44200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>69100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>62400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>102100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>101500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>116700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>110700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>117900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>98100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3322,56 +3453,59 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>174900</v>
+      </c>
+      <c r="E58" s="3">
         <v>152600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>146600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>148600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>133300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>144700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>139100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>97100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>65500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>54400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>73800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>76000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>61300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3387,50 +3521,53 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E59" s="3">
         <v>12600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>45100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>41900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>37400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>43400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3446,50 +3583,53 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>309500</v>
+      </c>
+      <c r="E60" s="3">
         <v>277900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>242000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>253900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>220300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>239600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>222200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>230000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>194400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>216100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>226400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>231300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>202800</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,50 +3645,53 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>466000</v>
+      </c>
+      <c r="E61" s="3">
         <v>436300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>434300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>389200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>334100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>286600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>217500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>250200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>228500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>162500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>164700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>310300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>311700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3564,8 +3707,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3573,41 +3719,41 @@
         <v>1300</v>
       </c>
       <c r="E62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F62" s="3">
         <v>2000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>44400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>46300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>46400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>38300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>63400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>51600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>80900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>59900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>31700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>34900</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,8 +3769,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,50 +3955,53 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>793500</v>
+      </c>
+      <c r="E66" s="3">
         <v>730400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>692800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>700800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>617400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>583600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>490600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>561500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>485400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>462000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>453700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>576200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>552300</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3859,8 +4017,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,50 +4165,53 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>273900</v>
+        <v>273800</v>
       </c>
       <c r="E70" s="3">
         <v>273900</v>
       </c>
       <c r="F70" s="3">
+        <v>273900</v>
+      </c>
+      <c r="G70" s="3">
         <v>274000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>274100</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>274200</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>274300</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>275000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>275100</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>274900</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>273600</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>295800</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>288600</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,50 +4289,53 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-470100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-442900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-418300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-404100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-386300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-362600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-342600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-359200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-332400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-328000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-296400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-276200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-263300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4351,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,50 +4537,53 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E76" s="3">
         <v>97500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>110300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>81500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>91700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>113700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>126200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-14300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-210500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-195500</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4413,8 +4599,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-14300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-32900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10100</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-12200</v>
       </c>
       <c r="S81" s="3">
         <v>-12200</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+      <c r="T81" s="3">
+        <v>-12200</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,67 +4816,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E83" s="3">
         <v>6000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4200</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4300</v>
       </c>
       <c r="K83" s="3">
         <v>4300</v>
       </c>
       <c r="L83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="M83" s="3">
         <v>6400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>6000</v>
       </c>
       <c r="O83" s="3">
         <v>6000</v>
       </c>
       <c r="P83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>7100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>6100</v>
       </c>
       <c r="R83" s="3">
         <v>6100</v>
       </c>
       <c r="S83" s="3">
+        <v>6100</v>
+      </c>
+      <c r="T83" s="3">
         <v>6200</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E89" s="3">
         <v>2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-39500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-25100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-38400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>11100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1300</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,67 +5274,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-36300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-36200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-68900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-43100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-65800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-40300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4200</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,67 +5458,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-35800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-68900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-43100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-67100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-36100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-54400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3700</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5342,8 +5576,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,181 +5792,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>72300</v>
+      </c>
+      <c r="E100" s="3">
         <v>5300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>43000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>71400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>37000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>21100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>126800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>50000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>46400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>96900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>13600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>41700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>7700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3200</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-200</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-100</v>
       </c>
       <c r="G101" s="3">
         <v>-100</v>
       </c>
       <c r="H101" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="I101" s="3">
         <v>-200</v>
       </c>
       <c r="J101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-200</v>
       </c>
       <c r="M101" s="3">
         <v>-200</v>
       </c>
       <c r="N101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E102" s="3">
         <v>2900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-24100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>20000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-69100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>77400</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-4700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1700</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>WEST</t>
   </si>
@@ -656,288 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>280900</v>
+      </c>
+      <c r="E8" s="3">
         <v>213800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>229000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>220900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>208400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>192500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>215000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>219600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>224700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>205400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>227700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>230300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>223400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>186400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>190400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>181300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>171100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>155300</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>239500</v>
+      </c>
+      <c r="E9" s="3">
         <v>184700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>191000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>183800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>167000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>155200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>180100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>184500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>189000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>171100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>193400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>189200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>184500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>148000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>150700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>143000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>136800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>122200</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E10" s="3">
         <v>29100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>38000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>37100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>41400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>37300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>34800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>35100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>35700</v>
-      </c>
-      <c r="L10" s="3">
-        <v>34300</v>
       </c>
       <c r="M10" s="3">
         <v>34300</v>
       </c>
       <c r="N10" s="3">
+        <v>34300</v>
+      </c>
+      <c r="O10" s="3">
         <v>41100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>38900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>38400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>39700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>38300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>34300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>33100</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,103 +1101,109 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E14" s="3">
         <v>1800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>5100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E15" s="3">
         <v>11800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5900</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>293400</v>
+      </c>
+      <c r="E17" s="3">
         <v>225100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>233900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>229900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>218600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>199700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>218900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>221600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>223100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>205300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>226700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>224800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>222100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>185600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>188400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>177200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>169500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>155200</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,318 +1410,334 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-24600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-24100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-100</v>
       </c>
       <c r="R20" s="3">
         <v>-100</v>
       </c>
       <c r="S20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E21" s="3">
         <v>800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>29000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E22" s="3">
         <v>12600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7400</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-22100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-22400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-17900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-23100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-20600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E24" s="3">
         <v>1800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-5200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-900</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-27200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-24600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-23700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-31900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3900</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-6100</v>
       </c>
       <c r="T26" s="3">
         <v>-6100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>-6100</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-27100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-23600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-22800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-32900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-11700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10100</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-12200</v>
       </c>
       <c r="T27" s="3">
         <v>-12200</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>-12200</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>24600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>24100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>100</v>
       </c>
       <c r="R32" s="3">
         <v>100</v>
       </c>
       <c r="S32" s="3">
+        <v>100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-27200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-23700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-20100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-32900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-11700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10100</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-12200</v>
       </c>
       <c r="T33" s="3">
         <v>-12200</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>-12200</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-27200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-23700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-20100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-32900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-11700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10100</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-12200</v>
       </c>
       <c r="T35" s="3">
         <v>-12200</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>-12200</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,53 +2570,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E41" s="3">
         <v>33100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>24300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>44400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>25200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>91000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11900</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,8 +2633,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2579,20 +2669,20 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>15100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>15700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>18200</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2602,59 +2692,62 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>85700</v>
+      </c>
+      <c r="E43" s="3">
         <v>83400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>100800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>102700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>102100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>90200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>99500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>99600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>115500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>101600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>98400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>96000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>94400</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2664,59 +2757,62 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>194200</v>
+      </c>
+      <c r="E44" s="3">
         <v>187400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>163300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>160600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>163700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>140400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>149900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>161300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>154700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>142600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>145800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>162200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>155300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>137600</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2726,59 +2822,62 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E45" s="3">
         <v>35900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>19700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>16700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>26900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>18400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>18700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14500</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,53 +2893,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>376600</v>
+      </c>
+      <c r="E46" s="3">
         <v>363800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>333600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>336600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>332500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>273200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>313100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>339600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>316200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>310300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>298100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>380100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>294100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>276600</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,8 +2958,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2865,31 +2970,31 @@
         <v>1000</v>
       </c>
       <c r="E47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F47" s="3">
         <v>1200</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1000</v>
       </c>
       <c r="G47" s="3">
         <v>1000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
+      <c r="H47" s="3">
+        <v>1000</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>1500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2912,59 +3017,62 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>0</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>542600</v>
+      </c>
+      <c r="E48" s="3">
         <v>539100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>530400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>500000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>480900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>464800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>411600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>302300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>255500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>210800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>196300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>145000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>143100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>143300</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2974,59 +3082,62 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>227000</v>
+      </c>
+      <c r="E49" s="3">
         <v>229000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>231000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>233100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>235100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>237100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>239100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>241400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>243400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>245100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>244900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>218000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>219600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>221300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3036,14 +3147,17 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,53 +3283,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E52" s="3">
         <v>4400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,53 +3413,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1157500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1138700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1101800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1077100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1056400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>983300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>971500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>891100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>822300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>773300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>746200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>750100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>661400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>645400</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,53 +3530,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E57" s="3">
         <v>67300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>84300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>52300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>43100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>44200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>69100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>62400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>102100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>101500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>116700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>110700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>117900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>98100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3456,59 +3587,62 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>195100</v>
+      </c>
+      <c r="E58" s="3">
         <v>174900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>152600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>146600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>148600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>133300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>144700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>139100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>97100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>65500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>54400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>73800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>76000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>61300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3524,53 +3658,56 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E59" s="3">
         <v>36600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>45100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>41900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>37400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>43400</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,53 +3723,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>361400</v>
+      </c>
+      <c r="E60" s="3">
         <v>309500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>277900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>242000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>253900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>220300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>239600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>222200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>230000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>194400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>216100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>226400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>231300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>202800</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,53 +3788,56 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>486900</v>
+      </c>
+      <c r="E61" s="3">
         <v>466000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>436300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>434300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>389200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>334100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>286600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>217500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>250200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>228500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>162500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>164700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>310300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>311700</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3710,53 +3853,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="E62" s="3">
         <v>1300</v>
       </c>
       <c r="F62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G62" s="3">
         <v>2000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>44400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>46300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>46400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>38300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>63400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>51600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>80900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>59900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>31700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>34900</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,53 +4113,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>865600</v>
+      </c>
+      <c r="E66" s="3">
         <v>793500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>730400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>692800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>700800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>617400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>583600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>490600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>561500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>485400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>462000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>453700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>576200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>552300</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4020,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,53 +4333,56 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>273700</v>
+      </c>
+      <c r="E70" s="3">
         <v>273800</v>
-      </c>
-      <c r="E70" s="3">
-        <v>273900</v>
       </c>
       <c r="F70" s="3">
         <v>273900</v>
       </c>
       <c r="G70" s="3">
+        <v>273900</v>
+      </c>
+      <c r="H70" s="3">
         <v>274000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>274100</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>274200</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>274300</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>275000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>275100</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>274900</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>273600</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>295800</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>288600</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,53 +4463,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-491700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-470100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-442900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-418300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-404100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-386300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-362600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-342600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-359200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-332400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-328000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-296400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-276200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-263300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4354,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,53 +4723,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E76" s="3">
         <v>71400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>97500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>110300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>81500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>91700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>113700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>126200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-14300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-210500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-195500</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4602,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-27200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-23700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-20100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-32900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-11700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10100</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-12200</v>
       </c>
       <c r="T81" s="3">
         <v>-12200</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>-12200</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,70 +5015,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E83" s="3">
         <v>5500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4300</v>
       </c>
       <c r="L83" s="3">
         <v>4300</v>
       </c>
       <c r="M83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="N83" s="3">
         <v>6400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>6000</v>
       </c>
       <c r="P83" s="3">
         <v>6000</v>
       </c>
       <c r="Q83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="R83" s="3">
         <v>7100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>6100</v>
       </c>
       <c r="S83" s="3">
         <v>6100</v>
       </c>
       <c r="T83" s="3">
+        <v>6100</v>
+      </c>
+      <c r="U83" s="3">
         <v>6200</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-22100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-23700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-39500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-25100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>11100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,70 +5495,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-41300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-36300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-36200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-68900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-43100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-65800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-36100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-40300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4200</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-40800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-35600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-35800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-68900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-43100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-67100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-36100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-54400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3700</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5579,8 +5813,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,190 +6038,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E100" s="3">
         <v>72300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>43000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>71400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>37000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>21100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>126800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>50000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>46400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>96900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>13600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>41700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>8500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>7700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3200</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-200</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-100</v>
       </c>
       <c r="H101" s="3">
         <v>-100</v>
       </c>
       <c r="I101" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="J101" s="3">
         <v>-200</v>
       </c>
       <c r="K101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-200</v>
       </c>
       <c r="N101" s="3">
         <v>-200</v>
       </c>
       <c r="O101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E102" s="3">
         <v>9300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-24100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>20000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-69100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>77400</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1700</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>WEST</t>
   </si>
@@ -656,314 +656,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>339500</v>
+      </c>
+      <c r="E8" s="3">
         <v>354800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>280900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>213800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>229000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>220900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>208400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>192500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>215000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>219600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>224700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>205400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>227700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>230300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>223400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>186400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>190400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>181300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>171100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>155300</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>300600</v>
+      </c>
+      <c r="E9" s="3">
         <v>313400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>239500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>184700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>191000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>183800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>167000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>155200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>180100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>184500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>189000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>171100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>193400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>189200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>184500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>148000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>150700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>143000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>136800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>122200</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>41400</v>
+        <v>38900</v>
       </c>
       <c r="E10" s="3">
         <v>41400</v>
       </c>
       <c r="F10" s="3">
+        <v>41400</v>
+      </c>
+      <c r="G10" s="3">
         <v>29100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>38000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>37100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>41400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>37300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>34800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>35100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>35700</v>
-      </c>
-      <c r="N10" s="3">
-        <v>34300</v>
       </c>
       <c r="O10" s="3">
         <v>34300</v>
       </c>
       <c r="P10" s="3">
+        <v>34300</v>
+      </c>
+      <c r="Q10" s="3">
         <v>41100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>38900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>38400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>39700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>38300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>34300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>33100</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1000,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1069,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,115 +1140,121 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>5100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E15" s="3">
         <v>13900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>15000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>6200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5900</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1260,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>344800</v>
+      </c>
+      <c r="E17" s="3">
         <v>360400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>293400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>225100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>233900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>229900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>218600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>199700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>218900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>221600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>223100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>205300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>226700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>224800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>222100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>185600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>188400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>177200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>169500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>155200</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>100</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,348 +1477,364 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-24600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>11900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-24100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-100</v>
       </c>
       <c r="T20" s="3">
         <v>-100</v>
       </c>
       <c r="U20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E21" s="3">
         <v>11700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>29000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>9000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6600</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E22" s="3">
         <v>14000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>13400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7400</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-21900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-22100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-22400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-7100</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-4600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-5200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-900</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-21600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-27200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-24600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-23700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-31900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3900</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-6100</v>
       </c>
       <c r="V26" s="3">
         <v>-6100</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+      <c r="W26" s="3">
+        <v>-6100</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-21500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-27100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-24500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-23600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-22800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-32900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-11600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10100</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-12200</v>
       </c>
       <c r="V27" s="3">
         <v>-12200</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
+      <c r="W27" s="3">
+        <v>-12200</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2327,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
         <v>3400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>24600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-11900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>24100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>100</v>
       </c>
       <c r="T32" s="3">
         <v>100</v>
       </c>
       <c r="U32" s="3">
+        <v>100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-27200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-24600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-32900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-12900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-11600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10100</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-12200</v>
       </c>
       <c r="V33" s="3">
         <v>-12200</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
+      <c r="W33" s="3">
+        <v>-12200</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-27200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-24600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-32900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-12900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-11600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10100</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-12200</v>
       </c>
       <c r="V35" s="3">
         <v>-12200</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
+      <c r="W35" s="3">
+        <v>-12200</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,59 +2743,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E41" s="3">
         <v>34000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>44000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>22400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>24300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>37200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>44400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>23700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>91000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11900</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2726,8 +2812,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2765,20 +2854,20 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>15100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>13700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>15700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>18200</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2788,65 +2877,68 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>97700</v>
+        <v>95100</v>
       </c>
       <c r="E43" s="3">
+        <v>99100</v>
+      </c>
+      <c r="F43" s="3">
         <v>85700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>83400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>102700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>102100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>90200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>99500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>99600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>100900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>115500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>101600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>98400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>96000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>94400</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,65 +2948,68 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>199800</v>
+      </c>
+      <c r="E44" s="3">
         <v>213000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>194200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>187400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>163300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>160600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>163700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>140400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>149900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>161300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>154700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>142600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>145800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>162200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>155300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>137600</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2924,65 +3019,68 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E45" s="3">
         <v>14000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>35900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>19700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>16700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>26900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>18400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>18700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14500</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,59 +3096,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>396400</v>
+      </c>
+      <c r="E46" s="3">
         <v>393600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>376600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>363800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>333600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>336600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>332500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>273200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>313100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>339600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>316200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>310300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>298100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>380100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>294100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>276600</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3066,13 +3167,16 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1000</v>
+        <v>7500</v>
       </c>
       <c r="E47" s="3">
         <v>1000</v>
@@ -3081,31 +3185,31 @@
         <v>1000</v>
       </c>
       <c r="G47" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H47" s="3">
         <v>1000</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I47" s="3">
         <v>1000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+      <c r="J47" s="3">
+        <v>1000</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>1500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3128,65 +3232,68 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
+      <c r="W47" s="3">
+        <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>543900</v>
+      </c>
+      <c r="E48" s="3">
         <v>546100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>542600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>539100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>530400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>500000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>480900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>464800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>411600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>302300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>255500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>210800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>196300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>145000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>143100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>143300</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3196,65 +3303,68 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>223300</v>
+      </c>
+      <c r="E49" s="3">
         <v>225100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>227000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>229000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>231000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>233100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>235100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>237100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>239100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>241400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>243400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>245100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>244900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>218000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>219600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>221300</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3264,14 +3374,17 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,59 +3522,62 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E52" s="3">
         <v>10800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4400</v>
       </c>
-      <c r="G52" s="3">
-        <v>4600</v>
-      </c>
       <c r="H52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I52" s="3">
         <v>5400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3593,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,59 +3664,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1176000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1178000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1157500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1138700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1101800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1077100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1056400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>983300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>971500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>891100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>822300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>773300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>746200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>750100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>661400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>645400</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3735,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,59 +3791,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>91200</v>
+      </c>
+      <c r="E57" s="3">
         <v>75700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>75800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>67300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>84300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>52300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>44200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>69100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>102100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>101500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>116700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>110700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>117900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>98100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,65 +3854,68 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>203400</v>
+      </c>
+      <c r="E58" s="3">
         <v>205400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>195100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>174900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>152600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>146600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>148600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>133300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>144700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>139100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>97100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>65500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>54400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>73800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>76000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>61300</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3798,59 +3931,62 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E59" s="3">
         <v>42500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>45000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>36600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>45100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>41900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>37400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>43400</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,59 +4002,62 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>413600</v>
+      </c>
+      <c r="E60" s="3">
         <v>384500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>361400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>309500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>277900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>242000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>253900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>220300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>239600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>222200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>230000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>194400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>216100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>226400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>231300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>202800</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,59 +4073,62 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>479700</v>
+      </c>
+      <c r="E61" s="3">
         <v>492000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>486900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>466000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>436300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>434300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>389200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>334100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>286600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>217500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>250200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>228500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>162500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>164700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>310300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>311700</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4002,59 +4144,62 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E62" s="3">
         <v>1000</v>
       </c>
       <c r="F62" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="G62" s="3">
         <v>1300</v>
       </c>
       <c r="H62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>44400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>46300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>46400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>38300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>63400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>51600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>80900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>59900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>31700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>34900</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,8 +4215,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,59 +4428,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>904300</v>
+      </c>
+      <c r="E66" s="3">
         <v>893000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>865600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>793500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>730400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>692800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>700800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>617400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>583600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>490600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>561500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>485400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>462000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>453700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>576200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>552300</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,8 +4499,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,59 +4668,62 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>273500</v>
+      </c>
+      <c r="E70" s="3">
         <v>273600</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>273700</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>273800</v>
-      </c>
-      <c r="G70" s="3">
-        <v>273900</v>
       </c>
       <c r="H70" s="3">
         <v>273900</v>
       </c>
       <c r="I70" s="3">
+        <v>273900</v>
+      </c>
+      <c r="J70" s="3">
         <v>274000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>274100</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>274200</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>274300</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>275000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>275100</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>274900</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>273600</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>295800</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>288600</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,59 +4810,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-534400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-510800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-491700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-470100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-442900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-418300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-404100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-386300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-362600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-342600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-359200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-332400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-328000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-296400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-276200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-263300</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4708,8 +4881,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,59 +5094,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E76" s="3">
         <v>11400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>71400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>97500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>110300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>81500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>91700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>113700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>126200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-14300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-210500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-195500</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5165,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-27200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-24600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-32900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-12900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-11600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10100</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-12200</v>
       </c>
       <c r="V81" s="3">
         <v>-12200</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
+      <c r="W81" s="3">
+        <v>-12200</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,76 +5412,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E83" s="3">
         <v>5700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>4300</v>
       </c>
       <c r="N83" s="3">
         <v>4300</v>
       </c>
       <c r="O83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="P83" s="3">
         <v>6400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5800</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>6000</v>
       </c>
       <c r="R83" s="3">
         <v>6000</v>
       </c>
       <c r="S83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="T83" s="3">
         <v>7100</v>
-      </c>
-      <c r="T83" s="3">
-        <v>6100</v>
       </c>
       <c r="U83" s="3">
         <v>6100</v>
       </c>
       <c r="V83" s="3">
+        <v>6100</v>
+      </c>
+      <c r="W83" s="3">
         <v>6200</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-26600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-22100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-23700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-39500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-25100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-38400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>11100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1300</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5936,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-41300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-18200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-36300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-68900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-43100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-65800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-36100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-40300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4200</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6147,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-23200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-40800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-35600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-35800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-68900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-43100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-67100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-36100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-54400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3700</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6053,8 +6286,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6083,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,208 +6529,220 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E100" s="3">
         <v>36900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>37600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>72300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>43000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>71400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>37000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>21100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>126800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>50000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>46400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-17500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>96900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>13600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>41700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>8500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>7700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3200</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-200</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-100</v>
       </c>
       <c r="J101" s="3">
         <v>-100</v>
       </c>
       <c r="K101" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="L101" s="3">
         <v>-200</v>
       </c>
       <c r="M101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-200</v>
       </c>
       <c r="P101" s="3">
         <v>-200</v>
       </c>
       <c r="Q101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-24100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-69100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>77400</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-4700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1700</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WEST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="92">
   <si>
     <t>WEST</t>
   </si>
@@ -656,326 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>308800</v>
+      </c>
+      <c r="E8" s="3">
         <v>339500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>354800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>280900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>213800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>229000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>220900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>208400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>192500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>215000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>219600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>224700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>205400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>227700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>230300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>223400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>186400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>190400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>181300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>171100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>155300</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>263100</v>
+      </c>
+      <c r="E9" s="3">
         <v>300600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>313400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>239500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>184700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>191000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>183800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>167000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>155200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>180100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>184500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>189000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>171100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>193400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>189200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>184500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>148000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>150700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>143000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>136800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>122200</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E10" s="3">
         <v>38900</v>
-      </c>
-      <c r="E10" s="3">
-        <v>41400</v>
       </c>
       <c r="F10" s="3">
         <v>41400</v>
       </c>
       <c r="G10" s="3">
+        <v>41400</v>
+      </c>
+      <c r="H10" s="3">
         <v>29100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>38000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>37100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>41400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>37300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>34800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>35100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>35700</v>
-      </c>
-      <c r="O10" s="3">
-        <v>34300</v>
       </c>
       <c r="P10" s="3">
         <v>34300</v>
       </c>
       <c r="Q10" s="3">
+        <v>34300</v>
+      </c>
+      <c r="R10" s="3">
         <v>41100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>38900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>38400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>39700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>38300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>34300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>33100</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1072,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,121 +1160,127 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E14" s="3">
         <v>3400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E15" s="3">
         <v>15200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>15000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>6400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5900</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1285,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>300900</v>
+      </c>
+      <c r="E17" s="3">
         <v>344800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>360400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>293400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>225100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>233900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>229900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>218600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>199700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>218900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>221600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>223100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>205300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>226700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>224800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>222100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>185600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>188400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>177200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>169500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>155200</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>100</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,363 +1511,379 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E20" s="3">
         <v>900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-24600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>11900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-24100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-100</v>
       </c>
       <c r="U20" s="3">
         <v>-100</v>
       </c>
       <c r="V20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E21" s="3">
         <v>9000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>29000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-16600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>10000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6600</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E22" s="3">
         <v>16000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>7400</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-25400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-22100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-22400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-17900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-23100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-7100</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-5200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-900</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-22600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-21600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-27200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-24600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-23700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-31900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3900</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-6100</v>
       </c>
       <c r="W26" s="3">
         <v>-6100</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
+      <c r="X26" s="3">
+        <v>-6100</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-22500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-27100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-24500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-23600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-22800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-32900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10100</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-12200</v>
       </c>
       <c r="W27" s="3">
         <v>-12200</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
+      <c r="X27" s="3">
+        <v>-12200</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,150 +2397,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>24600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-11900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>24100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
-      </c>
-      <c r="T32" s="3">
-        <v>100</v>
       </c>
       <c r="U32" s="3">
         <v>100</v>
       </c>
       <c r="V32" s="3">
+        <v>100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-22600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-21600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-27200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-24600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-23700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-26800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-32900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10100</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-12200</v>
       </c>
       <c r="W33" s="3">
         <v>-12200</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
+      <c r="X33" s="3">
+        <v>-12200</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-22600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-21600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-27200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-24600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-23700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-26800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-32900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10100</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-12200</v>
       </c>
       <c r="W35" s="3">
         <v>-12200</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
+      <c r="X35" s="3">
+        <v>-12200</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,62 +2830,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E41" s="3">
         <v>49900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>34000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>44000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>22400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>37200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>44400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>91000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>14300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11900</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,8 +2902,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2857,20 +2947,20 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>15100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>15700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>18200</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2880,68 +2970,71 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>83200</v>
+      </c>
+      <c r="E43" s="3">
         <v>95100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>99100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>85700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>83400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>100800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>102700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>102100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>90200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>99500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>99600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>100900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>115500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>101600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>98400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>96000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>94400</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2951,68 +3044,71 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>180800</v>
+      </c>
+      <c r="E44" s="3">
         <v>199800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>213000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>194200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>187400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>163300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>160600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>163700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>140400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>149900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>161300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>154700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>142600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>145800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>162200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>155300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>137600</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3022,68 +3118,71 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E45" s="3">
         <v>16200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>14000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>35900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>19700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>16700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>18400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>18700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14500</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3099,62 +3198,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>344000</v>
+      </c>
+      <c r="E46" s="3">
         <v>396400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>393600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>376600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>363800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>333600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>336600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>332500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>273200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>313100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>339600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>316200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>310300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>298100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>380100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>294100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>276600</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,16 +3272,19 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E47" s="3">
         <v>7500</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1000</v>
       </c>
       <c r="F47" s="3">
         <v>1000</v>
@@ -3187,32 +3292,32 @@
       <c r="G47" s="3">
         <v>1000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="H47" s="3">
         <v>1000</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J47" s="3">
         <v>1000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
+      <c r="K47" s="3">
+        <v>1000</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>1500</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3235,68 +3340,71 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
+      <c r="X47" s="3">
+        <v>0</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>535200</v>
+      </c>
+      <c r="E48" s="3">
         <v>543900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>546100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>542600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>539100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>530400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>500000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>480900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>464800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>411600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>302300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>255500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>210800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>196300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>145000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>143100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>143300</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3306,68 +3414,71 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>221300</v>
+      </c>
+      <c r="E49" s="3">
         <v>223300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>225100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>227000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>229000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>231000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>233100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>235100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>237100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>239100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>241400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>243400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>245100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>244900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>218000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>219600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>221300</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3377,14 +3488,17 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,62 +3642,65 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E52" s="3">
         <v>5000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3596,8 +3716,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,62 +3790,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1115800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1176000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1178000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1157500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1138700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1101800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1077100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1056400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>983300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>971500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>891100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>822300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>773300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>746200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>750100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>661400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>645400</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,8 +3864,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,62 +3922,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>85200</v>
+      </c>
+      <c r="E57" s="3">
         <v>91200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>75700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>75800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>67300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>84300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>52300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>43100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>44200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>69100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>102100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>101500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>116700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>110700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>117900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>98100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3857,68 +3988,71 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>186000</v>
+      </c>
+      <c r="E58" s="3">
         <v>203400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>205400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>195100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>174900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>152600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>146600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>148600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>133300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>144700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>139100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>97100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>65500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>54400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>73800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>76000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>61300</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,62 +4068,65 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E59" s="3">
         <v>28600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>45000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>36600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>45100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>41900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>37400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>43400</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4005,62 +4142,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>353900</v>
+      </c>
+      <c r="E60" s="3">
         <v>413600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>384500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>361400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>309500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>277900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>242000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>253900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>220300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>239600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>222200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>230000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>194400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>216100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>226400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>231300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>202800</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4076,62 +4216,65 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>496800</v>
+      </c>
+      <c r="E61" s="3">
         <v>479700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>492000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>486900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>466000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>436300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>434300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>389200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>334100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>286600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>217500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>250200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>228500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>162500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>164700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>310300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>311700</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4147,8 +4290,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4156,53 +4302,53 @@
         <v>900</v>
       </c>
       <c r="E62" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="F62" s="3">
         <v>1000</v>
       </c>
       <c r="G62" s="3">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="H62" s="3">
         <v>1300</v>
       </c>
       <c r="I62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J62" s="3">
         <v>2000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>44400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>46300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>46400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>38300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>63400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>51600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>80900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>59900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>31700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>34900</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4364,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,62 +4586,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>862600</v>
+      </c>
+      <c r="E66" s="3">
         <v>904300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>893000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>865600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>793500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>730400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>692800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>700800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>617400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>583600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>490600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>561500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>485400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>462000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>453700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>576200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>552300</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,8 +4660,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,62 +4836,65 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>273400</v>
+      </c>
+      <c r="E70" s="3">
         <v>273500</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>273600</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>273700</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>273800</v>
-      </c>
-      <c r="H70" s="3">
-        <v>273900</v>
       </c>
       <c r="I70" s="3">
         <v>273900</v>
       </c>
       <c r="J70" s="3">
+        <v>273900</v>
+      </c>
+      <c r="K70" s="3">
         <v>274000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>274100</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>274200</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>274300</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>275000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>275100</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>274900</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>273600</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>295800</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>288600</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,62 +4984,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-542900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-534400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-510800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-491700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-470100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-442900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-418300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-404100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-386300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-362600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-342600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-359200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-332400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-328000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-296400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-276200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-263300</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4884,8 +5058,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,62 +5280,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>71400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>97500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>110300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>81500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>91700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>113700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>126200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-14300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-210500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-195500</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5168,8 +5354,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-22600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-21600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-27200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-24600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-23700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-26800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-32900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10100</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-12200</v>
       </c>
       <c r="W81" s="3">
         <v>-12200</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
+      <c r="X81" s="3">
+        <v>-12200</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,79 +5611,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E83" s="3">
         <v>9500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>4300</v>
       </c>
       <c r="O83" s="3">
         <v>4300</v>
       </c>
       <c r="P83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Q83" s="3">
         <v>6400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5800</v>
-      </c>
-      <c r="R83" s="3">
-        <v>6000</v>
       </c>
       <c r="S83" s="3">
         <v>6000</v>
       </c>
       <c r="T83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="U83" s="3">
         <v>7100</v>
-      </c>
-      <c r="U83" s="3">
-        <v>6100</v>
       </c>
       <c r="V83" s="3">
         <v>6100</v>
       </c>
       <c r="W83" s="3">
+        <v>6100</v>
+      </c>
+      <c r="X83" s="3">
         <v>6200</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E89" s="3">
         <v>36700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-26600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-22100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-23700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>11100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-39500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-25100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-38400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>11100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1300</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,79 +6157,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-41300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-68900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-43100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-65800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-36100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-40300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-12600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4200</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-40800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-35600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-35800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-68900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-43100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-67100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-36100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-54400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3700</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6289,8 +6523,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,217 +6775,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>36900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>37600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>72300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>43000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>71400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>37000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>21100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>126800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>50000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>46400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>96900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>13600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>41700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>8500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>7700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3200</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-100</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
       </c>
       <c r="L101" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="M101" s="3">
         <v>-200</v>
       </c>
       <c r="N101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-200</v>
       </c>
       <c r="Q101" s="3">
         <v>-200</v>
       </c>
       <c r="R101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E102" s="3">
         <v>22700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-24100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>20000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-69100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>77400</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-4700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1700</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
